--- a/salidas/empresas/MRVL.xlsx
+++ b/salidas/empresas/MRVL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>29.11884689331055</v>
+        <v>29.11883354187012</v>
       </c>
       <c r="C2" t="n">
         <v>34.20999908447266</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>26.05459403991699</v>
+        <v>26.05459785461426</v>
       </c>
       <c r="C3" t="n">
         <v>30.61000061035156</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>23.02439498901367</v>
+        <v>23.02440452575684</v>
       </c>
       <c r="C4" t="n">
         <v>27.04999923706055</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>24.29690933227539</v>
+        <v>24.29691505432129</v>
       </c>
       <c r="C5" t="n">
         <v>28.54500007629395</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>20.28784942626953</v>
+        <v>20.2878532409668</v>
       </c>
       <c r="C6" t="n">
         <v>23.83499908447266</v>
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>15.78937244415283</v>
+        <v>15.78937721252441</v>
       </c>
       <c r="C8" t="n">
         <v>18.54999923706055</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>14.90415477752686</v>
+        <v>14.90414714813232</v>
       </c>
       <c r="C9" t="n">
         <v>17.51000022888184</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>16.48734283447266</v>
+        <v>16.48734092712402</v>
       </c>
       <c r="C10" t="n">
         <v>19.3700008392334</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>15.55955505371094</v>
+        <v>15.55956172943115</v>
       </c>
       <c r="C11" t="n">
         <v>18.28000068664551</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>17.54279518127441</v>
+        <v>17.54280090332031</v>
       </c>
       <c r="C12" t="n">
         <v>20.61000061035156</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>16.33412933349609</v>
+        <v>16.33412170410156</v>
       </c>
       <c r="C13" t="n">
         <v>19.19000053405762</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>15.56806945800781</v>
+        <v>15.56807231903076</v>
       </c>
       <c r="C14" t="n">
         <v>18.29000091552734</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>17.46620178222656</v>
+        <v>17.4661979675293</v>
       </c>
       <c r="C15" t="n">
         <v>20.52000045776367</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>14.30831527709961</v>
+        <v>14.30832195281982</v>
       </c>
       <c r="C16" t="n">
         <v>16.80999946594238</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>13.73803520202637</v>
+        <v>13.73803329467773</v>
       </c>
       <c r="C17" t="n">
         <v>16.13999938964844</v>
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>15.49997711181641</v>
+        <v>15.49996662139893</v>
       </c>
       <c r="C19" t="n">
         <v>18.20999908447266</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>15.32122707366943</v>
+        <v>15.32122421264648</v>
       </c>
       <c r="C20" t="n">
         <v>18</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>14.10404014587402</v>
+        <v>14.10404205322266</v>
       </c>
       <c r="C21" t="n">
         <v>16.56999969482422</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>13.93380165100098</v>
+        <v>13.93380355834961</v>
       </c>
       <c r="C22" t="n">
         <v>16.3700008392334</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>15.34675598144531</v>
+        <v>15.34676265716553</v>
       </c>
       <c r="C23" t="n">
         <v>18.03000068664551</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>12.71661472320557</v>
+        <v>12.71661567687988</v>
       </c>
       <c r="C24" t="n">
         <v>14.9399995803833</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>11.89948654174805</v>
+        <v>11.89948177337646</v>
       </c>
       <c r="C25" t="n">
         <v>13.97999954223633</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>10.10349559783936</v>
+        <v>10.1034984588623</v>
       </c>
       <c r="C26" t="n">
         <v>11.86999988555908</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>9.626835823059082</v>
+        <v>9.626837730407715</v>
       </c>
       <c r="C27" t="n">
         <v>11.3100004196167</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>9.260829925537109</v>
+        <v>9.260828018188477</v>
       </c>
       <c r="C28" t="n">
         <v>10.88000011444092</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>11.02276706695557</v>
+        <v>11.02276611328125</v>
       </c>
       <c r="C29" t="n">
         <v>12.94999980926514</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>14.77646923065186</v>
+        <v>14.77646636962891</v>
       </c>
       <c r="C30" t="n">
         <v>17.36000061035156</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>15.03182506561279</v>
+        <v>15.03182601928711</v>
       </c>
       <c r="C31" t="n">
         <v>17.65999984741211</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>12.58893871307373</v>
+        <v>12.58893775939941</v>
       </c>
       <c r="C32" t="n">
         <v>14.78999996185303</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>12.01013565063477</v>
+        <v>12.0101375579834</v>
       </c>
       <c r="C33" t="n">
         <v>14.10999965667725</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>7.915961265563965</v>
+        <v>7.915968894958496</v>
       </c>
       <c r="C34" t="n">
         <v>9.300000190734863</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>5.92420768737793</v>
+        <v>5.924206733703613</v>
       </c>
       <c r="C35" t="n">
         <v>6.960000038146973</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>4.936839580535889</v>
+        <v>4.936838626861572</v>
       </c>
       <c r="C36" t="n">
         <v>5.800000190734863</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>5.677364826202393</v>
+        <v>5.677365779876709</v>
       </c>
       <c r="C37" t="n">
         <v>6.670000076293945</v>
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>6.392356395721436</v>
+        <v>6.392354965209961</v>
       </c>
       <c r="C39" t="n">
         <v>7.510000228881836</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>7.796800136566162</v>
+        <v>7.796801090240479</v>
       </c>
       <c r="C40" t="n">
         <v>9.159999847412109</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>9.345944404602051</v>
+        <v>9.345946311950684</v>
       </c>
       <c r="C41" t="n">
         <v>10.97999954223633</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>9.728977203369141</v>
+        <v>9.728975296020508</v>
       </c>
       <c r="C42" t="n">
         <v>11.43000030517578</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>9.90772819519043</v>
+        <v>9.907729148864746</v>
       </c>
       <c r="C43" t="n">
         <v>11.64000034332275</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>11.35472965240479</v>
+        <v>11.35473155975342</v>
       </c>
       <c r="C44" t="n">
         <v>13.34000015258789</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>12.98048210144043</v>
+        <v>12.9804859161377</v>
       </c>
       <c r="C45" t="n">
         <v>15.25</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>13.78059196472168</v>
+        <v>13.78059005737305</v>
       </c>
       <c r="C46" t="n">
         <v>16.19000053405762</v>
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>11.68669033050537</v>
+        <v>11.686692237854</v>
       </c>
       <c r="C47" t="n">
         <v>13.72999954223633</v>
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>13.12518119812012</v>
+        <v>13.12518310546875</v>
       </c>
       <c r="C48" t="n">
         <v>15.42000007629395</v>
@@ -1375,11 +1387,11 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>17.66196823120117</v>
+        <v>17.6619701385498</v>
       </c>
       <c r="C49" t="n">
         <v>20.75</v>
@@ -1394,11 +1406,11 @@
       <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>14.8360538482666</v>
+        <v>14.83605670928955</v>
       </c>
       <c r="C50" t="n">
         <v>17.43000030517578</v>
@@ -1413,11 +1425,11 @@
       <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>16.44478607177734</v>
+        <v>16.44478225708008</v>
       </c>
       <c r="C51" t="n">
         <v>19.31999969482422</v>
@@ -1432,11 +1444,11 @@
       <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>17.38106918334961</v>
+        <v>17.38107681274414</v>
       </c>
       <c r="C52" t="n">
         <v>20.42000007629395</v>
@@ -1451,11 +1463,11 @@
       <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>17.58535575866699</v>
+        <v>17.58536148071289</v>
       </c>
       <c r="C53" t="n">
         <v>20.65999984741211</v>
@@ -1470,11 +1482,11 @@
       <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>16.15537261962891</v>
+        <v>16.15538024902344</v>
       </c>
       <c r="C54" t="n">
         <v>18.97999954223633</v>
@@ -1489,11 +1501,11 @@
       <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>13.41458225250244</v>
+        <v>13.41458320617676</v>
       </c>
       <c r="C55" t="n">
         <v>15.76000022888184</v>
@@ -1508,11 +1520,11 @@
       <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>12.69959259033203</v>
+        <v>12.6995964050293</v>
       </c>
       <c r="C56" t="n">
         <v>14.92000007629395</v>
@@ -1527,11 +1539,11 @@
       <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>13.54226303100586</v>
+        <v>13.54225826263428</v>
       </c>
       <c r="C57" t="n">
         <v>15.90999984741211</v>
@@ -1546,11 +1558,11 @@
       <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>14.90415477752686</v>
+        <v>14.90414714813232</v>
       </c>
       <c r="C58" t="n">
         <v>17.51000022888184</v>
@@ -1565,11 +1577,11 @@
       <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>16.41073608398438</v>
+        <v>16.41073226928711</v>
       </c>
       <c r="C59" t="n">
         <v>19.28000068664551</v>
@@ -1584,11 +1596,11 @@
       <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>16.41073608398438</v>
+        <v>16.41073226928711</v>
       </c>
       <c r="C60" t="n">
         <v>19.28000068664551</v>
@@ -1603,11 +1615,11 @@
       <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>15.78937244415283</v>
+        <v>15.78937721252441</v>
       </c>
       <c r="C61" t="n">
         <v>18.54999923706055</v>
@@ -1622,11 +1634,11 @@
       <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>16.18091773986816</v>
+        <v>16.1809139251709</v>
       </c>
       <c r="C62" t="n">
         <v>19.01000022888184</v>
@@ -1641,11 +1653,11 @@
       <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>15.55955505371094</v>
+        <v>15.55956172943115</v>
       </c>
       <c r="C63" t="n">
         <v>18.28000068664551</v>
@@ -1660,11 +1672,11 @@
       <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>13.23583698272705</v>
+        <v>13.23583221435547</v>
       </c>
       <c r="C64" t="n">
         <v>15.55000019073486</v>
@@ -1679,11 +1691,11 @@
       <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>13.13369560241699</v>
+        <v>13.13369750976562</v>
       </c>
       <c r="C65" t="n">
         <v>15.43000030517578</v>
@@ -1698,11 +1710,11 @@
       <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>13.82315063476562</v>
+        <v>13.82314872741699</v>
       </c>
       <c r="C66" t="n">
         <v>16.23999977111816</v>
@@ -1717,7 +1729,7 @@
       <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1736,11 +1748,11 @@
       <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>12.61447238922119</v>
+        <v>12.61447620391846</v>
       </c>
       <c r="C68" t="n">
         <v>14.81999969482422</v>
@@ -1755,7 +1767,7 @@
       <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1774,11 +1786,11 @@
       <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>12.35912036895752</v>
+        <v>12.35912322998047</v>
       </c>
       <c r="C70" t="n">
         <v>14.52000045776367</v>
@@ -1793,11 +1805,11 @@
       <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>11.90799808502197</v>
+        <v>11.90799427032471</v>
       </c>
       <c r="C71" t="n">
         <v>13.98999977111816</v>
@@ -1812,11 +1824,11 @@
       <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>12.01865005493164</v>
+        <v>12.01865196228027</v>
       </c>
       <c r="C72" t="n">
         <v>14.11999988555908</v>
@@ -1831,11 +1843,11 @@
       <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>11.78883647918701</v>
+        <v>11.78883266448975</v>
       </c>
       <c r="C73" t="n">
         <v>13.85000038146973</v>
@@ -1850,11 +1862,11 @@
       <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>13.22732543945312</v>
+        <v>13.22732639312744</v>
       </c>
       <c r="C74" t="n">
         <v>15.53999996185303</v>
@@ -1869,11 +1881,11 @@
       <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>12.76769065856934</v>
+        <v>12.76768779754639</v>
       </c>
       <c r="C75" t="n">
         <v>15</v>
@@ -1888,11 +1900,11 @@
       <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>13.38904571533203</v>
+        <v>13.38905239105225</v>
       </c>
       <c r="C76" t="n">
         <v>15.72999954223633</v>
@@ -1907,11 +1919,11 @@
       <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>12.77619934082031</v>
+        <v>12.77620124816895</v>
       </c>
       <c r="C77" t="n">
         <v>15.01000022888184</v>
@@ -1926,7 +1938,7 @@
       <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -1945,11 +1957,11 @@
       <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>9.649547576904297</v>
+        <v>9.64954662322998</v>
       </c>
       <c r="C79" t="n">
         <v>11.27999973297119</v>
@@ -1964,11 +1976,11 @@
       <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>9.632439613342285</v>
+        <v>9.632436752319336</v>
       </c>
       <c r="C80" t="n">
         <v>11.26000022888184</v>
@@ -1983,11 +1995,11 @@
       <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>8.691437721252441</v>
+        <v>8.691439628601074</v>
       </c>
       <c r="C81" t="n">
         <v>10.15999984741211</v>
@@ -2002,11 +2014,11 @@
       <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>7.88230037689209</v>
+        <v>7.882303714752197</v>
       </c>
       <c r="C82" t="n">
         <v>9.159999847412109</v>
@@ -2021,11 +2033,11 @@
       <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>6.789451122283936</v>
+        <v>6.789449214935303</v>
       </c>
       <c r="C83" t="n">
         <v>7.889999866485596</v>
@@ -2040,11 +2052,11 @@
       <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>7.288547992706299</v>
+        <v>7.288549900054932</v>
       </c>
       <c r="C84" t="n">
         <v>8.470000267028809</v>
@@ -2059,11 +2071,11 @@
       <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>6.291065216064453</v>
+        <v>6.29106616973877</v>
       </c>
       <c r="C85" t="n">
         <v>7.260000228881836</v>
@@ -2078,11 +2090,11 @@
       <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>8.015470504760742</v>
+        <v>8.015476226806641</v>
       </c>
       <c r="C86" t="n">
         <v>9.25</v>
@@ -2097,11 +2109,11 @@
       <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>8.752035140991211</v>
+        <v>8.752033233642578</v>
       </c>
       <c r="C87" t="n">
         <v>10.10000038146973</v>
@@ -2116,11 +2128,11 @@
       <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>9.219721794128418</v>
+        <v>9.219715118408203</v>
       </c>
       <c r="C88" t="n">
         <v>10.57999992370605</v>
@@ -2135,11 +2147,11 @@
       <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>9.376577377319336</v>
+        <v>9.37657642364502</v>
       </c>
       <c r="C89" t="n">
         <v>10.76000022888184</v>
@@ -2154,11 +2166,11 @@
       <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>9.455004692077637</v>
+        <v>9.45500373840332</v>
       </c>
       <c r="C90" t="n">
         <v>10.85000038146973</v>
@@ -2173,11 +2185,11 @@
       <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>10.25964164733887</v>
+        <v>10.25964546203613</v>
       </c>
       <c r="C91" t="n">
         <v>11.71000003814697</v>
@@ -2192,11 +2204,11 @@
       <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>11.37234687805176</v>
+        <v>11.37234401702881</v>
       </c>
       <c r="C92" t="n">
         <v>12.97999954223633</v>
@@ -2211,7 +2223,7 @@
       <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2230,11 +2242,11 @@
       <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>10.12397766113281</v>
+        <v>10.12397480010986</v>
       </c>
       <c r="C94" t="n">
         <v>11.5</v>
@@ -2249,11 +2261,11 @@
       <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>10.56414794921875</v>
+        <v>10.56414985656738</v>
       </c>
       <c r="C95" t="n">
         <v>12</v>
@@ -2268,11 +2280,11 @@
       <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>12.52732086181641</v>
+        <v>12.52732181549072</v>
       </c>
       <c r="C96" t="n">
         <v>14.22999954223633</v>
@@ -2287,7 +2299,7 @@
       <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2306,11 +2318,11 @@
       <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>13.20258903503418</v>
+        <v>13.20259284973145</v>
       </c>
       <c r="C98" t="n">
         <v>14.93000030517578</v>
@@ -2325,11 +2337,11 @@
       <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>13.52093982696533</v>
+        <v>13.5209436416626</v>
       </c>
       <c r="C99" t="n">
         <v>15.28999996185303</v>
@@ -2344,7 +2356,7 @@
       <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2363,11 +2375,11 @@
       <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>14.07917404174805</v>
+        <v>14.0791711807251</v>
       </c>
       <c r="C101" t="n">
         <v>15.85999965667725</v>
@@ -2382,11 +2394,11 @@
       <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>13.82174015045166</v>
+        <v>13.82173633575439</v>
       </c>
       <c r="C102" t="n">
         <v>15.56999969482422</v>
@@ -2401,11 +2413,11 @@
       <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>12.77260684967041</v>
+        <v>12.77261161804199</v>
       </c>
       <c r="C103" t="n">
         <v>14.32999992370605</v>
@@ -2420,7 +2432,7 @@
       <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2439,11 +2451,11 @@
       <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>12.39825630187988</v>
+        <v>12.39825439453125</v>
       </c>
       <c r="C105" t="n">
         <v>13.90999984741211</v>
@@ -2458,11 +2470,11 @@
       <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>12.06662559509277</v>
+        <v>12.06662940979004</v>
       </c>
       <c r="C106" t="n">
         <v>13.47999954223633</v>
@@ -2477,11 +2489,11 @@
       <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>12.0308198928833</v>
+        <v>12.03082180023193</v>
       </c>
       <c r="C107" t="n">
         <v>13.4399995803833</v>
@@ -2496,11 +2508,11 @@
       <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>12.81855297088623</v>
+        <v>12.81855487823486</v>
       </c>
       <c r="C108" t="n">
         <v>14.31999969482422</v>
@@ -2515,11 +2527,11 @@
       <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>13.03102016448975</v>
+        <v>13.03102111816406</v>
       </c>
       <c r="C109" t="n">
         <v>14.5</v>
@@ -2534,11 +2546,11 @@
       <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>13.92072105407715</v>
+        <v>13.92072200775146</v>
       </c>
       <c r="C110" t="n">
         <v>15.48999977111816</v>
@@ -2553,11 +2565,11 @@
       <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>14.48690032958984</v>
+        <v>14.48689460754395</v>
       </c>
       <c r="C111" t="n">
         <v>16.1200008392334</v>
@@ -2572,11 +2584,11 @@
       <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>13.2589693069458</v>
+        <v>13.25897121429443</v>
       </c>
       <c r="C112" t="n">
         <v>14.69999980926514</v>
@@ -2591,11 +2603,11 @@
       <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>12.63660907745361</v>
+        <v>12.63661289215088</v>
       </c>
       <c r="C113" t="n">
         <v>14.01000022888184</v>
@@ -2610,11 +2622,11 @@
       <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>12.61856937408447</v>
+        <v>12.61857128143311</v>
       </c>
       <c r="C114" t="n">
         <v>13.98999977111816</v>
@@ -2629,11 +2641,11 @@
       <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>11.94860935211182</v>
+        <v>11.94860744476318</v>
       </c>
       <c r="C115" t="n">
         <v>13.1899995803833</v>
@@ -2648,11 +2660,11 @@
       <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>11.26919460296631</v>
+        <v>11.26919651031494</v>
       </c>
       <c r="C116" t="n">
         <v>12.4399995803833</v>
@@ -2667,7 +2679,7 @@
       <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -2686,11 +2698,11 @@
       <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>8.198246955871582</v>
+        <v>8.198249816894531</v>
       </c>
       <c r="C118" t="n">
         <v>9.050000190734863</v>
@@ -2705,11 +2717,11 @@
       <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>7.486507892608643</v>
+        <v>7.486507415771484</v>
       </c>
       <c r="C119" t="n">
         <v>8.210000038146973</v>
@@ -2724,11 +2736,11 @@
       <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>8.079226493835449</v>
+        <v>8.079227447509766</v>
       </c>
       <c r="C120" t="n">
         <v>8.859999656677246</v>
@@ -2743,7 +2755,7 @@
       <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -2762,11 +2774,11 @@
       <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>8.129373550415039</v>
+        <v>8.129374504089355</v>
       </c>
       <c r="C122" t="n">
         <v>8.850000381469727</v>
@@ -2781,11 +2793,11 @@
       <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>8.77237606048584</v>
+        <v>8.772373199462891</v>
       </c>
       <c r="C123" t="n">
         <v>9.550000190734863</v>
@@ -2800,11 +2812,11 @@
       <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>9.526041030883789</v>
+        <v>9.526036262512207</v>
       </c>
       <c r="C124" t="n">
         <v>10.3100004196167</v>
@@ -2819,11 +2831,11 @@
       <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>9.22113037109375</v>
+        <v>9.221131324768066</v>
       </c>
       <c r="C125" t="n">
         <v>9.979999542236328</v>
@@ -2838,11 +2850,11 @@
       <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>9.452122688293457</v>
+        <v>9.452117919921875</v>
       </c>
       <c r="C126" t="n">
         <v>10.22999954223633</v>
@@ -2857,11 +2869,11 @@
       <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>8.857145309448242</v>
+        <v>8.857141494750977</v>
       </c>
       <c r="C127" t="n">
         <v>9.529999732971191</v>
@@ -2876,11 +2888,11 @@
       <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>10.92040538787842</v>
+        <v>10.92040157318115</v>
       </c>
       <c r="C128" t="n">
         <v>11.75</v>
@@ -2895,11 +2907,11 @@
       <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>11.52451038360596</v>
+        <v>11.52450847625732</v>
       </c>
       <c r="C129" t="n">
         <v>12.39999961853027</v>
@@ -2914,11 +2926,11 @@
       <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>12.39022636413574</v>
+        <v>12.39022827148438</v>
       </c>
       <c r="C130" t="n">
         <v>13.27000045776367</v>
@@ -2933,11 +2945,11 @@
       <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>12.1661376953125</v>
+        <v>12.16613578796387</v>
       </c>
       <c r="C131" t="n">
         <v>13.02999973297119</v>
@@ -2952,11 +2964,11 @@
       <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>13.3892879486084</v>
+        <v>13.38928699493408</v>
       </c>
       <c r="C132" t="n">
         <v>14.34000015258789</v>
@@ -2971,11 +2983,11 @@
       <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>13.00627136230469</v>
+        <v>13.00626850128174</v>
       </c>
       <c r="C133" t="n">
         <v>13.86999988555908</v>
@@ -2990,11 +3002,11 @@
       <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>13.94399738311768</v>
+        <v>13.94399547576904</v>
       </c>
       <c r="C134" t="n">
         <v>14.86999988555908</v>
@@ -3009,11 +3021,11 @@
       <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>14.62853622436523</v>
+        <v>14.6285343170166</v>
       </c>
       <c r="C135" t="n">
         <v>15.60000038146973</v>
@@ -3028,11 +3040,11 @@
       <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>14.36492252349854</v>
+        <v>14.36492443084717</v>
       </c>
       <c r="C136" t="n">
         <v>15.26000022888184</v>
@@ -3047,7 +3059,7 @@
       <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3066,11 +3078,11 @@
       <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>16.22878456115723</v>
+        <v>16.22878646850586</v>
       </c>
       <c r="C138" t="n">
         <v>17.23999977111816</v>
@@ -3085,11 +3097,11 @@
       <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>15.60665321350098</v>
+        <v>15.60666465759277</v>
       </c>
       <c r="C139" t="n">
         <v>16.52000045776367</v>
@@ -3104,11 +3116,11 @@
       <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>14.69972991943359</v>
+        <v>14.69973373413086</v>
       </c>
       <c r="C140" t="n">
         <v>15.5600004196167</v>
@@ -3123,7 +3135,7 @@
       <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -3142,11 +3154,11 @@
       <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>16.91036415100098</v>
+        <v>16.91035652160645</v>
       </c>
       <c r="C142" t="n">
         <v>17.89999961853027</v>
@@ -3161,11 +3173,11 @@
       <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>17.50601959228516</v>
+        <v>17.50601768493652</v>
       </c>
       <c r="C143" t="n">
         <v>18.46999931335449</v>
@@ -3180,11 +3192,11 @@
       <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>21.17404556274414</v>
+        <v>21.17404365539551</v>
       </c>
       <c r="C144" t="n">
         <v>22.34000015258789</v>
@@ -3199,7 +3211,7 @@
       <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -3218,7 +3230,7 @@
       <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -3237,11 +3249,11 @@
       <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>22.32487869262695</v>
+        <v>22.32488059997559</v>
       </c>
       <c r="C147" t="n">
         <v>23.48999977111816</v>
@@ -3256,11 +3268,11 @@
       <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>20.01452827453613</v>
+        <v>20.0145263671875</v>
       </c>
       <c r="C148" t="n">
         <v>21</v>
@@ -3275,11 +3287,11 @@
       <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>19.11863899230957</v>
+        <v>19.11863327026367</v>
       </c>
       <c r="C149" t="n">
         <v>20.05999946594238</v>
@@ -3294,7 +3306,7 @@
       <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -3313,11 +3325,11 @@
       <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>20.43388557434082</v>
+        <v>20.43388748168945</v>
       </c>
       <c r="C151" t="n">
         <v>21.44000053405762</v>
@@ -3332,11 +3344,11 @@
       <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>20.36724472045898</v>
+        <v>20.36724662780762</v>
       </c>
       <c r="C152" t="n">
         <v>21.30999946594238</v>
@@ -3351,11 +3363,11 @@
       <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>19.76511383056641</v>
+        <v>19.76511764526367</v>
       </c>
       <c r="C153" t="n">
         <v>20.68000030517578</v>
@@ -3370,11 +3382,11 @@
       <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>18.44616508483887</v>
+        <v>18.44617080688477</v>
       </c>
       <c r="C154" t="n">
         <v>19.29999923706055</v>
@@ -3389,11 +3401,11 @@
       <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>15.73293209075928</v>
+        <v>15.73293399810791</v>
       </c>
       <c r="C155" t="n">
         <v>16.40999984741211</v>
@@ -3408,11 +3420,11 @@
       <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>15.44531154632568</v>
+        <v>15.44530963897705</v>
       </c>
       <c r="C156" t="n">
         <v>16.11000061035156</v>
@@ -3427,11 +3439,11 @@
       <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>15.58481121063232</v>
+        <v>15.58480930328369</v>
       </c>
       <c r="C157" t="n">
         <v>16.19000053405762</v>
@@ -3446,7 +3458,7 @@
       <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -3465,11 +3477,11 @@
       <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>19.20425605773926</v>
+        <v>19.20425796508789</v>
       </c>
       <c r="C159" t="n">
         <v>19.95000076293945</v>
@@ -3484,11 +3496,11 @@
       <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>19.14649391174316</v>
+        <v>19.14650344848633</v>
       </c>
       <c r="C160" t="n">
         <v>19.88999938964844</v>
@@ -3503,7 +3515,7 @@
       <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -3522,7 +3534,7 @@
       <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -3541,11 +3553,11 @@
       <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>23.04601287841797</v>
+        <v>23.0460147857666</v>
       </c>
       <c r="C163" t="n">
         <v>23.8700008392334</v>
@@ -3560,11 +3572,11 @@
       <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>25.41426277160645</v>
+        <v>25.41426086425781</v>
       </c>
       <c r="C164" t="n">
         <v>26.26000022888184</v>
@@ -3579,11 +3591,11 @@
       <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>23.1980152130127</v>
+        <v>23.19801330566406</v>
       </c>
       <c r="C165" t="n">
         <v>23.96999931335449</v>
@@ -3598,11 +3610,11 @@
       <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>24.16581153869629</v>
+        <v>24.16580200195312</v>
       </c>
       <c r="C166" t="n">
         <v>24.96999931335449</v>
@@ -3617,11 +3629,11 @@
       <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>23.66636276245117</v>
+        <v>23.66636657714844</v>
       </c>
       <c r="C167" t="n">
         <v>24.38999938964844</v>
@@ -3636,11 +3648,11 @@
       <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>25.58761405944824</v>
+        <v>25.58761596679688</v>
       </c>
       <c r="C168" t="n">
         <v>26.3700008392334</v>
@@ -3655,11 +3667,11 @@
       <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>25.83045959472656</v>
+        <v>25.83046340942383</v>
       </c>
       <c r="C169" t="n">
         <v>26.55999946594238</v>
@@ -3674,11 +3686,11 @@
       <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>23.37967872619629</v>
+        <v>23.37968063354492</v>
       </c>
       <c r="C170" t="n">
         <v>24.04000091552734</v>
@@ -3693,11 +3705,11 @@
       <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>20.71493911743164</v>
+        <v>20.71494483947754</v>
       </c>
       <c r="C171" t="n">
         <v>21.29999923706055</v>
@@ -3712,11 +3724,11 @@
       <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>22.0084056854248</v>
+        <v>22.00840759277344</v>
       </c>
       <c r="C172" t="n">
         <v>22.6299991607666</v>
@@ -3731,11 +3743,11 @@
       <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>26.07781982421875</v>
+        <v>26.07781600952148</v>
       </c>
       <c r="C173" t="n">
         <v>26.73999977111816</v>
@@ -3750,11 +3762,11 @@
       <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>31.81220626831055</v>
+        <v>31.81221389770508</v>
       </c>
       <c r="C174" t="n">
         <v>32.61999893188477</v>
@@ -3769,11 +3781,11 @@
       <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>34.1917839050293</v>
+        <v>34.19178771972656</v>
       </c>
       <c r="C175" t="n">
         <v>35.06000137329102</v>
@@ -3788,11 +3800,11 @@
       <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>35.62295150756836</v>
+        <v>35.62294387817383</v>
       </c>
       <c r="C176" t="n">
         <v>36.47000122070312</v>
@@ -3807,11 +3819,11 @@
       <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>37.87929153442383</v>
+        <v>37.8792839050293</v>
       </c>
       <c r="C177" t="n">
         <v>38.77999877929688</v>
@@ -3826,11 +3838,11 @@
       <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>38.77791595458984</v>
+        <v>38.77791213989258</v>
       </c>
       <c r="C178" t="n">
         <v>39.70000076293945</v>
@@ -3845,7 +3857,7 @@
       <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -3864,7 +3876,7 @@
       <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -3883,11 +3895,11 @@
       <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>46.56041717529297</v>
+        <v>46.56040954589844</v>
       </c>
       <c r="C181" t="n">
         <v>47.54000091552734</v>
@@ -3902,7 +3914,7 @@
       <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -3921,11 +3933,11 @@
       <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>47.28516387939453</v>
+        <v>47.28517150878906</v>
       </c>
       <c r="C183" t="n">
         <v>48.27999877929688</v>
@@ -3940,11 +3952,11 @@
       <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>47.97074127197266</v>
+        <v>47.97073745727539</v>
       </c>
       <c r="C184" t="n">
         <v>48.97999954223633</v>
@@ -3959,11 +3971,11 @@
       <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>44.33124542236328</v>
+        <v>44.33124160766602</v>
       </c>
       <c r="C185" t="n">
         <v>45.20999908447266</v>
@@ -3978,11 +3990,11 @@
       <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>47.36117553710938</v>
+        <v>47.36118316650391</v>
       </c>
       <c r="C186" t="n">
         <v>48.29999923706055</v>
@@ -3997,11 +4009,11 @@
       <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>57.19622421264648</v>
+        <v>57.19623947143555</v>
       </c>
       <c r="C187" t="n">
         <v>58.33000183105469</v>
@@ -4022,11 +4034,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>59.39672470092773</v>
+        <v>59.396728515625</v>
       </c>
       <c r="C188" t="n">
         <v>60.5099983215332</v>
@@ -4047,7 +4059,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -4072,11 +4084,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>59.20040130615234</v>
+        <v>59.20040893554688</v>
       </c>
       <c r="C190" t="n">
         <v>60.31000137329102</v>
@@ -4097,7 +4109,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -4122,7 +4134,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -4147,11 +4159,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>85.96124267578125</v>
+        <v>85.96125030517578</v>
       </c>
       <c r="C193" t="n">
         <v>87.48999786376953</v>
@@ -4172,7 +4184,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -4197,11 +4209,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>67.18393707275391</v>
+        <v>67.18396759033203</v>
       </c>
       <c r="C195" t="n">
         <v>68.33000183105469</v>
@@ -4222,11 +4234,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>70.50727081298828</v>
+        <v>70.50730133056641</v>
       </c>
       <c r="C196" t="n">
         <v>71.70999908447266</v>
@@ -4249,11 +4261,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>57.15744781494141</v>
+        <v>57.15745544433594</v>
       </c>
       <c r="C197" t="n">
         <v>58.08000183105469</v>
@@ -4276,11 +4288,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>58.21044540405273</v>
+        <v>58.21044921875</v>
       </c>
       <c r="C198" t="n">
         <v>59.15000152587891</v>
@@ -4303,11 +4315,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>42.83855438232422</v>
+        <v>42.83856582641602</v>
       </c>
       <c r="C199" t="n">
         <v>43.52999877929688</v>
@@ -4330,11 +4342,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>54.87069702148438</v>
+        <v>54.87069320678711</v>
       </c>
       <c r="C200" t="n">
         <v>55.68000030517578</v>
@@ -4357,11 +4369,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>46.13947296142578</v>
+        <v>46.13947677612305</v>
       </c>
       <c r="C201" t="n">
         <v>46.81999969482422</v>
@@ -4384,11 +4396,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>42.28630828857422</v>
+        <v>42.28631210327148</v>
       </c>
       <c r="C202" t="n">
         <v>42.90999984741211</v>
@@ -4411,7 +4423,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -4438,7 +4450,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -4465,11 +4477,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>36.54698181152344</v>
+        <v>36.54697418212891</v>
       </c>
       <c r="C205" t="n">
         <v>37.04000091552734</v>
@@ -4492,7 +4504,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -4519,11 +4531,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>44.62215423583984</v>
+        <v>44.62215042114258</v>
       </c>
       <c r="C207" t="n">
         <v>45.15000152587891</v>
@@ -4546,11 +4558,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>42.79377365112305</v>
+        <v>42.79378509521484</v>
       </c>
       <c r="C208" t="n">
         <v>43.29999923706055</v>
@@ -4573,7 +4585,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -4600,11 +4612,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>57.89200592041016</v>
+        <v>57.89199829101562</v>
       </c>
       <c r="C210" t="n">
         <v>58.4900016784668</v>
@@ -4627,11 +4639,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>59.1688117980957</v>
+        <v>59.16880798339844</v>
       </c>
       <c r="C211" t="n">
         <v>59.77999877929688</v>
@@ -4654,11 +4666,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>64.52884674072266</v>
+        <v>64.52886199951172</v>
       </c>
       <c r="C212" t="n">
         <v>65.12999725341797</v>
@@ -4681,11 +4693,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>57.71234893798828</v>
+        <v>57.71235656738281</v>
       </c>
       <c r="C213" t="n">
         <v>58.25</v>
@@ -4708,11 +4720,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>53.6303825378418</v>
+        <v>53.63037872314453</v>
       </c>
       <c r="C214" t="n">
         <v>54.13000106811523</v>
@@ -4735,11 +4747,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>46.83687591552734</v>
+        <v>46.83687210083008</v>
       </c>
       <c r="C215" t="n">
         <v>47.22000122070312</v>
@@ -4762,11 +4774,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>55.27782821655273</v>
+        <v>55.27783203125</v>
       </c>
       <c r="C216" t="n">
         <v>55.72999954223633</v>
@@ -4789,11 +4801,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>59.82067489624023</v>
+        <v>59.82066345214844</v>
       </c>
       <c r="C217" t="n">
         <v>60.31000137329102</v>
@@ -4816,11 +4828,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>67.22174835205078</v>
+        <v>67.22176361083984</v>
       </c>
       <c r="C218" t="n">
         <v>67.69999694824219</v>
@@ -4843,11 +4855,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>71.15380096435547</v>
+        <v>71.15379333496094</v>
       </c>
       <c r="C219" t="n">
         <v>71.66000366210938</v>
@@ -4870,7 +4882,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -4897,11 +4909,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>65.49943542480469</v>
+        <v>65.49944305419922</v>
       </c>
       <c r="C221" t="n">
         <v>65.91000366210938</v>
@@ -4924,7 +4936,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -4951,11 +4963,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>69.46458435058594</v>
+        <v>69.46456909179688</v>
       </c>
       <c r="C223" t="n">
         <v>69.90000152587891</v>
@@ -4978,11 +4990,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>66.61814880371094</v>
+        <v>66.61814117431641</v>
       </c>
       <c r="C224" t="n">
         <v>66.98000335693359</v>
@@ -5005,11 +5017,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>75.82810974121094</v>
+        <v>75.82811737060547</v>
       </c>
       <c r="C225" t="n">
         <v>76.23999786376953</v>
@@ -5032,7 +5044,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -5059,11 +5071,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>79.7431640625</v>
+        <v>79.74315643310547</v>
       </c>
       <c r="C227" t="n">
         <v>80.11000061035156</v>
@@ -5086,7 +5098,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -5113,7 +5125,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -5140,11 +5152,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>112.4002456665039</v>
+        <v>112.4002304077148</v>
       </c>
       <c r="C230" t="n">
         <v>112.8600006103516</v>
@@ -5167,11 +5179,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>91.44595336914062</v>
+        <v>91.44596099853516</v>
       </c>
       <c r="C231" t="n">
         <v>91.81999969482422</v>
@@ -5194,11 +5206,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>61.31918716430664</v>
+        <v>61.31918334960938</v>
       </c>
       <c r="C232" t="n">
         <v>61.56999969482422</v>
@@ -5221,7 +5233,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -5248,11 +5260,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>60.01290893554688</v>
+        <v>60.01290512084961</v>
       </c>
       <c r="C234" t="n">
         <v>60.18999862670898</v>
@@ -5275,7 +5287,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -5302,11 +5314,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>80.19912719726562</v>
+        <v>80.19913482666016</v>
       </c>
       <c r="C236" t="n">
         <v>80.37000274658203</v>
@@ -5329,11 +5341,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>62.73633575439453</v>
+        <v>62.7363395690918</v>
       </c>
       <c r="C237" t="n">
         <v>62.86999893188477</v>
@@ -5356,7 +5368,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -5383,7 +5395,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -5410,11 +5422,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>89.26899719238281</v>
+        <v>89.26900482177734</v>
       </c>
       <c r="C240" t="n">
         <v>89.40000152587891</v>
@@ -5437,11 +5449,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>84.85547637939453</v>
+        <v>84.85548400878906</v>
       </c>
       <c r="C241" t="n">
         <v>84.98000335693359</v>
@@ -5466,7 +5478,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -5495,7 +5507,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -5524,7 +5536,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -5553,7 +5565,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -5582,7 +5594,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -5611,7 +5623,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -5640,7 +5652,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -5669,7 +5681,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -5698,32 +5710,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>260.8999938964844</v>
+        <v>258.9500122070312</v>
       </c>
       <c r="C250" t="n">
-        <v>260.8999938964844</v>
+        <v>258.9500122070312</v>
       </c>
       <c r="D250" t="n">
-        <v>303318600</v>
+        <v>316747200</v>
       </c>
       <c r="E250" t="n">
         <v>3.02</v>
       </c>
       <c r="F250" t="n">
-        <v>86.39072645578953</v>
+        <v>85.74503715464611</v>
       </c>
       <c r="G250" t="n">
         <v>876900000</v>
       </c>
       <c r="H250" t="n">
-        <v>228783204647.8271</v>
+        <v>227073265704.3457</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3458987341772152</v>
+        <v>0.3612124529592884</v>
       </c>
     </row>
   </sheetData>
@@ -5755,75 +5767,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>43863</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>43953</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>44356</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -5859,13 +5871,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>43954</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>44044</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -5901,13 +5913,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44045</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>44533</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -5943,13 +5955,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44136</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>44226</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>44630</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -5976,7 +5988,7 @@
       <c r="I5" t="n">
         <v>-0.4099999999999999</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>44630</v>
       </c>
       <c r="K5" t="n">
@@ -5989,13 +6001,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>44317</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>44356</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -6022,7 +6034,7 @@
       <c r="I6" t="n">
         <v>-0.3699999999999999</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>44630</v>
       </c>
       <c r="K6" t="n">
@@ -6035,13 +6047,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44318</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -6068,7 +6080,7 @@
       <c r="I7" t="n">
         <v>-0.47</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>44630</v>
       </c>
       <c r="K7" t="n">
@@ -6081,13 +6093,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>44499</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>44533</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -6114,7 +6126,7 @@
       <c r="I8" t="n">
         <v>-0.5199999999999999</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>44630</v>
       </c>
       <c r="K8" t="n">
@@ -6127,13 +6139,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>44590</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>44630</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -6160,7 +6172,7 @@
       <c r="I9" t="n">
         <v>-0.53</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>44630</v>
       </c>
       <c r="K9" t="n">
@@ -6173,13 +6185,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44591</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -6206,7 +6218,7 @@
       <c r="I10" t="n">
         <v>-0.6000000000000001</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="K10" t="n">
@@ -6219,13 +6231,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>44772</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>44799</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -6252,7 +6264,7 @@
       <c r="I11" t="n">
         <v>-0.25</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>44799</v>
       </c>
       <c r="K11" t="n">
@@ -6265,13 +6277,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>44863</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>44897</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -6298,7 +6310,7 @@
       <c r="I12" t="n">
         <v>-0.15</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>44897</v>
       </c>
       <c r="K12" t="n">
@@ -6311,13 +6323,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44864</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>44954</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>44994</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -6344,7 +6356,7 @@
       <c r="I13" t="n">
         <v>-0.19</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>44994</v>
       </c>
       <c r="K13" t="n">
@@ -6357,13 +6369,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44955</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>45045</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -6390,7 +6402,7 @@
       <c r="I14" t="n">
         <v>-0.19</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="K14" t="n">
@@ -6403,13 +6415,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>45136</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -6436,7 +6448,7 @@
       <c r="I15" t="n">
         <v>-0.4400000000000001</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="K15" t="n">
@@ -6449,13 +6461,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45137</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>45227</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -6482,7 +6494,7 @@
       <c r="I16" t="n">
         <v>-0.65</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="K16" t="n">
@@ -6495,13 +6507,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45228</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>45325</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>45364</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -6528,7 +6540,7 @@
       <c r="I17" t="n">
         <v>-1.08</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>45364</v>
       </c>
       <c r="K17" t="n">
@@ -6541,13 +6553,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45326</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>45416</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -6574,7 +6586,7 @@
       <c r="I18" t="n">
         <v>-1.13</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="K18" t="n">
@@ -6587,13 +6599,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45417</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>45507</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -6620,7 +6632,7 @@
       <c r="I19" t="n">
         <v>-1.11</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="K19" t="n">
@@ -6633,13 +6645,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45508</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>45598</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>45630</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -6666,7 +6678,7 @@
       <c r="I20" t="n">
         <v>-1.7</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>45630</v>
       </c>
       <c r="K20" t="n">
@@ -6679,13 +6691,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45599</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>45689</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>45728</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -6712,7 +6724,7 @@
       <c r="I21" t="n">
         <v>-1.02</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>45728</v>
       </c>
       <c r="K21" t="n">
@@ -6725,13 +6737,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45690</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>45780</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -6758,7 +6770,7 @@
       <c r="I22" t="n">
         <v>-0.5700000000000001</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="K22" t="n">
@@ -6771,13 +6783,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45781</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>45871</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -6804,7 +6816,7 @@
       <c r="I23" t="n">
         <v>-0.13</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="K23" t="n">
@@ -6817,13 +6829,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45872</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>45962</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>45994</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -6850,7 +6862,7 @@
       <c r="I24" t="n">
         <v>2.85</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>45994</v>
       </c>
       <c r="K24" t="n">
@@ -6863,13 +6875,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45963</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -6896,7 +6908,7 @@
       <c r="I25" t="n">
         <v>3.07</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="K25" t="n">
@@ -6909,13 +6921,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>46170</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -6942,7 +6954,7 @@
       <c r="I26" t="n">
         <v>2.91</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>46170</v>
       </c>
       <c r="K26" t="n">
@@ -6955,13 +6967,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>46235</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -6988,7 +7000,7 @@
       <c r="I27" t="n">
         <v>3.02</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="K27" t="n">
@@ -7025,52 +7037,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44349</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>44356</v>
       </c>
       <c r="C2" t="n">
@@ -7099,10 +7111,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44428</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="C3" t="n">
@@ -7131,10 +7143,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44526</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>44533</v>
       </c>
       <c r="C4" t="n">
@@ -7163,10 +7175,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44623</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>44630</v>
       </c>
       <c r="C5" t="n">
@@ -7195,10 +7207,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44701</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="C6" t="n">
@@ -7227,10 +7239,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44792</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>44799</v>
       </c>
       <c r="C7" t="n">
@@ -7259,10 +7271,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44890</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>44897</v>
       </c>
       <c r="C8" t="n">
@@ -7291,10 +7303,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44987</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>44994</v>
       </c>
       <c r="C9" t="n">
@@ -7323,10 +7335,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>45065</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="C10" t="n">
@@ -7355,10 +7367,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>45156</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="C11" t="n">
@@ -7387,10 +7399,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>45254</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="C12" t="n">
@@ -7419,10 +7431,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45357</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>45364</v>
       </c>
       <c r="C13" t="n">
@@ -7451,10 +7463,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45436</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="C14" t="n">
@@ -7483,10 +7495,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45527</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="C15" t="n">
@@ -7515,10 +7527,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45623</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>45630</v>
       </c>
       <c r="C16" t="n">
@@ -7547,10 +7559,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45721</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>45728</v>
       </c>
       <c r="C17" t="n">
@@ -7579,10 +7591,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45800</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="C18" t="n">
@@ -7611,10 +7623,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45891</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="C19" t="n">
@@ -7643,10 +7655,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45987</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>45994</v>
       </c>
       <c r="C20" t="n">
@@ -7675,10 +7687,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>46085</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="C21" t="n">
@@ -7707,10 +7719,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>46163</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>46170</v>
       </c>
       <c r="C22" t="n">
@@ -7739,10 +7751,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46255</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="C23" t="n">
@@ -7789,12 +7801,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/MRVL.xlsx
+++ b/salidas/empresas/MRVL.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>29.11883354187012</v>
+        <v>29.11883735656738</v>
       </c>
       <c r="C2" t="n">
         <v>34.20999908447266</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>26.05459785461426</v>
+        <v>26.05459594726562</v>
       </c>
       <c r="C3" t="n">
         <v>30.61000061035156</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>23.02440452575684</v>
+        <v>23.02439117431641</v>
       </c>
       <c r="C4" t="n">
         <v>27.04999923706055</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>20.2878532409668</v>
+        <v>20.28785705566406</v>
       </c>
       <c r="C6" t="n">
         <v>23.83499908447266</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>18.86638641357422</v>
+        <v>18.86639213562012</v>
       </c>
       <c r="C7" t="n">
         <v>22.16500091552734</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>15.78937721252441</v>
+        <v>15.78936958312988</v>
       </c>
       <c r="C8" t="n">
         <v>18.54999923706055</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>16.48734092712402</v>
+        <v>16.48733711242676</v>
       </c>
       <c r="C10" t="n">
         <v>19.3700008392334</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>15.55956172943115</v>
+        <v>15.55954933166504</v>
       </c>
       <c r="C11" t="n">
         <v>18.28000068664551</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>16.33412170410156</v>
+        <v>16.33412551879883</v>
       </c>
       <c r="C13" t="n">
         <v>19.19000053405762</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>15.56807231903076</v>
+        <v>15.56806945800781</v>
       </c>
       <c r="C14" t="n">
         <v>18.29000091552734</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>17.4661979675293</v>
+        <v>17.46619415283203</v>
       </c>
       <c r="C15" t="n">
         <v>20.52000045776367</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>14.30832195281982</v>
+        <v>14.30831909179688</v>
       </c>
       <c r="C16" t="n">
         <v>16.80999946594238</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>13.73803329467773</v>
+        <v>13.73803424835205</v>
       </c>
       <c r="C17" t="n">
         <v>16.13999938964844</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>15.49996662139893</v>
+        <v>15.49996757507324</v>
       </c>
       <c r="C19" t="n">
         <v>18.20999908447266</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>15.32122421264648</v>
+        <v>15.32122611999512</v>
       </c>
       <c r="C20" t="n">
         <v>18</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>14.10404205322266</v>
+        <v>14.10403919219971</v>
       </c>
       <c r="C21" t="n">
         <v>16.56999969482422</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>13.93380355834961</v>
+        <v>13.93380260467529</v>
       </c>
       <c r="C22" t="n">
         <v>16.3700008392334</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>15.34676265716553</v>
+        <v>15.34676456451416</v>
       </c>
       <c r="C23" t="n">
         <v>18.03000068664551</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>12.71661567687988</v>
+        <v>12.71661853790283</v>
       </c>
       <c r="C24" t="n">
         <v>14.9399995803833</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>11.89948177337646</v>
+        <v>11.8994836807251</v>
       </c>
       <c r="C25" t="n">
         <v>13.97999954223633</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>10.1034984588623</v>
+        <v>10.10350036621094</v>
       </c>
       <c r="C26" t="n">
         <v>11.86999988555908</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>9.626837730407715</v>
+        <v>9.626835823059082</v>
       </c>
       <c r="C27" t="n">
         <v>11.3100004196167</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>9.260828018188477</v>
+        <v>9.260830879211426</v>
       </c>
       <c r="C28" t="n">
         <v>10.88000011444092</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>11.02276611328125</v>
+        <v>11.02277278900146</v>
       </c>
       <c r="C29" t="n">
         <v>12.94999980926514</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>14.77646636962891</v>
+        <v>14.77647304534912</v>
       </c>
       <c r="C30" t="n">
         <v>17.36000061035156</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>15.03182601928711</v>
+        <v>15.03182506561279</v>
       </c>
       <c r="C31" t="n">
         <v>17.65999984741211</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>12.0101375579834</v>
+        <v>12.01013660430908</v>
       </c>
       <c r="C33" t="n">
         <v>14.10999965667725</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>7.915968894958496</v>
+        <v>7.915967464447021</v>
       </c>
       <c r="C34" t="n">
         <v>9.300000190734863</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>5.924206733703613</v>
+        <v>5.924206256866455</v>
       </c>
       <c r="C35" t="n">
         <v>6.960000038146973</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>5.677365779876709</v>
+        <v>5.677364826202393</v>
       </c>
       <c r="C37" t="n">
         <v>6.670000076293945</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>6.205095291137695</v>
+        <v>6.20509672164917</v>
       </c>
       <c r="C38" t="n">
         <v>7.289999961853027</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>6.392354965209961</v>
+        <v>6.392355918884277</v>
       </c>
       <c r="C39" t="n">
         <v>7.510000228881836</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>7.796801090240479</v>
+        <v>7.796802043914795</v>
       </c>
       <c r="C40" t="n">
         <v>9.159999847412109</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>9.345946311950684</v>
+        <v>9.345947265625</v>
       </c>
       <c r="C41" t="n">
         <v>10.97999954223633</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>9.728975296020508</v>
+        <v>9.728976249694824</v>
       </c>
       <c r="C42" t="n">
         <v>11.43000030517578</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>9.907729148864746</v>
+        <v>9.907724380493164</v>
       </c>
       <c r="C43" t="n">
         <v>11.64000034332275</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>11.35473155975342</v>
+        <v>11.35472965240479</v>
       </c>
       <c r="C44" t="n">
         <v>13.34000015258789</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>12.9804859161377</v>
+        <v>12.98048496246338</v>
       </c>
       <c r="C45" t="n">
         <v>15.25</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>13.78059005737305</v>
+        <v>13.780592918396</v>
       </c>
       <c r="C46" t="n">
         <v>16.19000053405762</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>11.686692237854</v>
+        <v>11.68668651580811</v>
       </c>
       <c r="C47" t="n">
         <v>13.72999954223633</v>
@@ -1391,7 +1391,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>17.6619701385498</v>
+        <v>17.66197204589844</v>
       </c>
       <c r="C49" t="n">
         <v>20.75</v>
@@ -1410,7 +1410,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>14.83605670928955</v>
+        <v>14.83605766296387</v>
       </c>
       <c r="C50" t="n">
         <v>17.43000030517578</v>
@@ -1429,7 +1429,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>16.44478225708008</v>
+        <v>16.44477844238281</v>
       </c>
       <c r="C51" t="n">
         <v>19.31999969482422</v>
@@ -1448,7 +1448,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>17.38107681274414</v>
+        <v>17.38107872009277</v>
       </c>
       <c r="C52" t="n">
         <v>20.42000007629395</v>
@@ -1467,7 +1467,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>17.58536148071289</v>
+        <v>17.58536529541016</v>
       </c>
       <c r="C53" t="n">
         <v>20.65999984741211</v>
@@ -1486,7 +1486,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>16.15538024902344</v>
+        <v>16.15537643432617</v>
       </c>
       <c r="C54" t="n">
         <v>18.97999954223633</v>
@@ -1505,7 +1505,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>13.41458320617676</v>
+        <v>13.41458606719971</v>
       </c>
       <c r="C55" t="n">
         <v>15.76000022888184</v>
@@ -1524,7 +1524,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>12.6995964050293</v>
+        <v>12.69959545135498</v>
       </c>
       <c r="C56" t="n">
         <v>14.92000007629395</v>
@@ -1543,7 +1543,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>13.54225826263428</v>
+        <v>13.54225921630859</v>
       </c>
       <c r="C57" t="n">
         <v>15.90999984741211</v>
@@ -1581,7 +1581,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>16.41073226928711</v>
+        <v>16.41073417663574</v>
       </c>
       <c r="C59" t="n">
         <v>19.28000068664551</v>
@@ -1600,7 +1600,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>16.41073226928711</v>
+        <v>16.41073417663574</v>
       </c>
       <c r="C60" t="n">
         <v>19.28000068664551</v>
@@ -1619,7 +1619,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>15.78937721252441</v>
+        <v>15.78936958312988</v>
       </c>
       <c r="C61" t="n">
         <v>18.54999923706055</v>
@@ -1638,7 +1638,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>16.1809139251709</v>
+        <v>16.1809196472168</v>
       </c>
       <c r="C62" t="n">
         <v>19.01000022888184</v>
@@ -1657,7 +1657,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>15.55956172943115</v>
+        <v>15.55954933166504</v>
       </c>
       <c r="C63" t="n">
         <v>18.28000068664551</v>
@@ -1676,7 +1676,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>13.23583221435547</v>
+        <v>13.2358341217041</v>
       </c>
       <c r="C64" t="n">
         <v>15.55000019073486</v>
@@ -1695,7 +1695,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>13.13369750976562</v>
+        <v>13.13369178771973</v>
       </c>
       <c r="C65" t="n">
         <v>15.43000030517578</v>
@@ -1714,7 +1714,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>13.82314872741699</v>
+        <v>13.82314777374268</v>
       </c>
       <c r="C66" t="n">
         <v>16.23999977111816</v>
@@ -1733,7 +1733,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>12.57191467285156</v>
+        <v>12.57192039489746</v>
       </c>
       <c r="C67" t="n">
         <v>14.77000045776367</v>
@@ -1752,7 +1752,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>12.61447620391846</v>
+        <v>12.61447334289551</v>
       </c>
       <c r="C68" t="n">
         <v>14.81999969482422</v>
@@ -1790,7 +1790,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>12.35912322998047</v>
+        <v>12.35912227630615</v>
       </c>
       <c r="C70" t="n">
         <v>14.52000045776367</v>
@@ -1809,7 +1809,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>11.90799427032471</v>
+        <v>11.90799713134766</v>
       </c>
       <c r="C71" t="n">
         <v>13.98999977111816</v>
@@ -1828,7 +1828,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>12.01865196228027</v>
+        <v>12.01865577697754</v>
       </c>
       <c r="C72" t="n">
         <v>14.11999988555908</v>
@@ -1847,7 +1847,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>11.78883266448975</v>
+        <v>11.78883075714111</v>
       </c>
       <c r="C73" t="n">
         <v>13.85000038146973</v>
@@ -1866,7 +1866,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>13.22732639312744</v>
+        <v>13.22732353210449</v>
       </c>
       <c r="C74" t="n">
         <v>15.53999996185303</v>
@@ -1961,7 +1961,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>9.64954662322998</v>
+        <v>9.649548530578613</v>
       </c>
       <c r="C79" t="n">
         <v>11.27999973297119</v>
@@ -1980,7 +1980,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>9.632436752319336</v>
+        <v>9.632437705993652</v>
       </c>
       <c r="C80" t="n">
         <v>11.26000022888184</v>
@@ -1999,7 +1999,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>8.691439628601074</v>
+        <v>8.691434860229492</v>
       </c>
       <c r="C81" t="n">
         <v>10.15999984741211</v>
@@ -2018,7 +2018,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>7.882303714752197</v>
+        <v>7.882298946380615</v>
       </c>
       <c r="C82" t="n">
         <v>9.159999847412109</v>
@@ -2037,7 +2037,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>6.789449214935303</v>
+        <v>6.789451122283936</v>
       </c>
       <c r="C83" t="n">
         <v>7.889999866485596</v>
@@ -2056,7 +2056,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>7.288549900054932</v>
+        <v>7.288546562194824</v>
       </c>
       <c r="C84" t="n">
         <v>8.470000267028809</v>
@@ -2075,7 +2075,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>6.29106616973877</v>
+        <v>6.291067600250244</v>
       </c>
       <c r="C85" t="n">
         <v>7.260000228881836</v>
@@ -2094,7 +2094,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>8.015476226806641</v>
+        <v>8.015474319458008</v>
       </c>
       <c r="C86" t="n">
         <v>9.25</v>
@@ -2113,7 +2113,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>8.752033233642578</v>
+        <v>8.752035140991211</v>
       </c>
       <c r="C87" t="n">
         <v>10.10000038146973</v>
@@ -2132,7 +2132,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>9.219715118408203</v>
+        <v>9.219717979431152</v>
       </c>
       <c r="C88" t="n">
         <v>10.57999992370605</v>
@@ -2151,7 +2151,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>9.37657642364502</v>
+        <v>9.376579284667969</v>
       </c>
       <c r="C89" t="n">
         <v>10.76000022888184</v>
@@ -2170,7 +2170,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>9.45500373840332</v>
+        <v>9.455007553100586</v>
       </c>
       <c r="C90" t="n">
         <v>10.85000038146973</v>
@@ -2189,7 +2189,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>10.25964546203613</v>
+        <v>10.2596435546875</v>
       </c>
       <c r="C91" t="n">
         <v>11.71000003814697</v>
@@ -2208,7 +2208,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>11.37234401702881</v>
+        <v>11.37234497070312</v>
       </c>
       <c r="C92" t="n">
         <v>12.97999954223633</v>
@@ -2227,7 +2227,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>10.6101016998291</v>
+        <v>10.61009979248047</v>
       </c>
       <c r="C93" t="n">
         <v>12.10999965667725</v>
@@ -2246,7 +2246,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>10.12397480010986</v>
+        <v>10.12397575378418</v>
       </c>
       <c r="C94" t="n">
         <v>11.5</v>
@@ -2265,7 +2265,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>10.56414985656738</v>
+        <v>10.5641508102417</v>
       </c>
       <c r="C95" t="n">
         <v>12</v>
@@ -2284,7 +2284,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>12.52732181549072</v>
+        <v>12.52731895446777</v>
       </c>
       <c r="C96" t="n">
         <v>14.22999954223633</v>
@@ -2303,7 +2303,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>12.71622562408447</v>
+        <v>12.71622657775879</v>
       </c>
       <c r="C97" t="n">
         <v>14.38000011444092</v>
@@ -2322,7 +2322,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>13.20259284973145</v>
+        <v>13.2025899887085</v>
       </c>
       <c r="C98" t="n">
         <v>14.93000030517578</v>
@@ -2341,7 +2341,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>13.5209436416626</v>
+        <v>13.52094078063965</v>
       </c>
       <c r="C99" t="n">
         <v>15.28999996185303</v>
@@ -2360,7 +2360,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>13.98152446746826</v>
+        <v>13.98152828216553</v>
       </c>
       <c r="C100" t="n">
         <v>15.75</v>
@@ -2379,7 +2379,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>14.0791711807251</v>
+        <v>14.07917404174805</v>
       </c>
       <c r="C101" t="n">
         <v>15.85999965667725</v>
@@ -2417,7 +2417,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>12.77261161804199</v>
+        <v>12.77261257171631</v>
       </c>
       <c r="C103" t="n">
         <v>14.32999992370605</v>
@@ -2436,7 +2436,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>11.89020538330078</v>
+        <v>11.89020156860352</v>
       </c>
       <c r="C104" t="n">
         <v>13.34000015258789</v>
@@ -2455,7 +2455,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>12.39825439453125</v>
+        <v>12.39825630187988</v>
       </c>
       <c r="C105" t="n">
         <v>13.90999984741211</v>
@@ -2474,7 +2474,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>12.06662940979004</v>
+        <v>12.06662750244141</v>
       </c>
       <c r="C106" t="n">
         <v>13.47999954223633</v>
@@ -2493,7 +2493,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>12.03082180023193</v>
+        <v>12.03082084655762</v>
       </c>
       <c r="C107" t="n">
         <v>13.4399995803833</v>
@@ -2512,7 +2512,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>12.81855487823486</v>
+        <v>12.81855297088623</v>
       </c>
       <c r="C108" t="n">
         <v>14.31999969482422</v>
@@ -2531,7 +2531,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>13.03102111816406</v>
+        <v>13.03102016448975</v>
       </c>
       <c r="C109" t="n">
         <v>14.5</v>
@@ -2569,7 +2569,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>14.48689460754395</v>
+        <v>14.48689842224121</v>
       </c>
       <c r="C111" t="n">
         <v>16.1200008392334</v>
@@ -2588,7 +2588,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>13.25897121429443</v>
+        <v>13.25897216796875</v>
       </c>
       <c r="C112" t="n">
         <v>14.69999980926514</v>
@@ -2626,7 +2626,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>12.61857128143311</v>
+        <v>12.61857223510742</v>
       </c>
       <c r="C114" t="n">
         <v>13.98999977111816</v>
@@ -2645,7 +2645,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>11.94860744476318</v>
+        <v>11.94860935211182</v>
       </c>
       <c r="C115" t="n">
         <v>13.1899995803833</v>
@@ -2664,7 +2664,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>11.26919651031494</v>
+        <v>11.26919937133789</v>
       </c>
       <c r="C116" t="n">
         <v>12.4399995803833</v>
@@ -2683,7 +2683,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>10.20931148529053</v>
+        <v>10.20931720733643</v>
       </c>
       <c r="C117" t="n">
         <v>11.27000045776367</v>
@@ -2702,7 +2702,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>8.198249816894531</v>
+        <v>8.198251724243164</v>
       </c>
       <c r="C118" t="n">
         <v>9.050000190734863</v>
@@ -2721,7 +2721,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>7.486507415771484</v>
+        <v>7.486509323120117</v>
       </c>
       <c r="C119" t="n">
         <v>8.210000038146973</v>
@@ -2740,7 +2740,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>8.079227447509766</v>
+        <v>8.079225540161133</v>
       </c>
       <c r="C120" t="n">
         <v>8.859999656677246</v>
@@ -2759,7 +2759,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>8.101819038391113</v>
+        <v>8.10181713104248</v>
       </c>
       <c r="C121" t="n">
         <v>8.819999694824219</v>
@@ -2797,7 +2797,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>8.772373199462891</v>
+        <v>8.772375106811523</v>
       </c>
       <c r="C123" t="n">
         <v>9.550000190734863</v>
@@ -2816,7 +2816,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>9.526036262512207</v>
+        <v>9.526040077209473</v>
       </c>
       <c r="C124" t="n">
         <v>10.3100004196167</v>
@@ -2835,7 +2835,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>9.221131324768066</v>
+        <v>9.221129417419434</v>
       </c>
       <c r="C125" t="n">
         <v>9.979999542236328</v>
@@ -2854,7 +2854,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>9.452117919921875</v>
+        <v>9.452118873596191</v>
       </c>
       <c r="C126" t="n">
         <v>10.22999954223633</v>
@@ -2892,7 +2892,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>10.92040157318115</v>
+        <v>10.9204044342041</v>
       </c>
       <c r="C128" t="n">
         <v>11.75</v>
@@ -2911,7 +2911,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>11.52450847625732</v>
+        <v>11.52451324462891</v>
       </c>
       <c r="C129" t="n">
         <v>12.39999961853027</v>
@@ -2930,7 +2930,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>12.39022827148438</v>
+        <v>12.39022636413574</v>
       </c>
       <c r="C130" t="n">
         <v>13.27000045776367</v>
@@ -2949,7 +2949,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>12.16613578796387</v>
+        <v>12.1661376953125</v>
       </c>
       <c r="C131" t="n">
         <v>13.02999973297119</v>
@@ -2987,7 +2987,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>13.00626850128174</v>
+        <v>13.00626659393311</v>
       </c>
       <c r="C133" t="n">
         <v>13.86999988555908</v>
@@ -3006,7 +3006,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>13.94399547576904</v>
+        <v>13.94399356842041</v>
       </c>
       <c r="C134" t="n">
         <v>14.86999988555908</v>
@@ -3025,7 +3025,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>14.6285343170166</v>
+        <v>14.62853622436523</v>
       </c>
       <c r="C135" t="n">
         <v>15.60000038146973</v>
@@ -3044,7 +3044,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>14.36492443084717</v>
+        <v>14.36492252349854</v>
       </c>
       <c r="C136" t="n">
         <v>15.26000022888184</v>
@@ -3082,7 +3082,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>16.22878646850586</v>
+        <v>16.22878837585449</v>
       </c>
       <c r="C138" t="n">
         <v>17.23999977111816</v>
@@ -3101,7 +3101,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>15.60666465759277</v>
+        <v>15.60665321350098</v>
       </c>
       <c r="C139" t="n">
         <v>16.52000045776367</v>
@@ -3120,7 +3120,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>14.69973373413086</v>
+        <v>14.69972991943359</v>
       </c>
       <c r="C140" t="n">
         <v>15.5600004196167</v>
@@ -3139,7 +3139,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>16.9198055267334</v>
+        <v>16.91980934143066</v>
       </c>
       <c r="C141" t="n">
         <v>17.90999984741211</v>
@@ -3158,7 +3158,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>16.91035652160645</v>
+        <v>16.91036224365234</v>
       </c>
       <c r="C142" t="n">
         <v>17.89999961853027</v>
@@ -3177,7 +3177,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>17.50601768493652</v>
+        <v>17.50602912902832</v>
       </c>
       <c r="C143" t="n">
         <v>18.46999931335449</v>
@@ -3196,7 +3196,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>21.17404365539551</v>
+        <v>21.17404174804688</v>
       </c>
       <c r="C144" t="n">
         <v>22.34000015258789</v>
@@ -3215,7 +3215,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>20.40507316589355</v>
+        <v>20.40508079528809</v>
       </c>
       <c r="C145" t="n">
         <v>21.46999931335449</v>
@@ -3234,7 +3234,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>22.17281532287598</v>
+        <v>22.17281723022461</v>
       </c>
       <c r="C146" t="n">
         <v>23.32999992370605</v>
@@ -3272,7 +3272,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>20.0145263671875</v>
+        <v>20.01452827453613</v>
       </c>
       <c r="C148" t="n">
         <v>21</v>
@@ -3291,7 +3291,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>19.11863327026367</v>
+        <v>19.11863708496094</v>
       </c>
       <c r="C149" t="n">
         <v>20.05999946594238</v>
@@ -3310,7 +3310,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>20.52918815612793</v>
+        <v>20.52919006347656</v>
       </c>
       <c r="C150" t="n">
         <v>21.54000091552734</v>
@@ -3329,7 +3329,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>20.43388748168945</v>
+        <v>20.43387985229492</v>
       </c>
       <c r="C151" t="n">
         <v>21.44000053405762</v>
@@ -3348,7 +3348,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>20.36724662780762</v>
+        <v>20.36724281311035</v>
       </c>
       <c r="C152" t="n">
         <v>21.30999946594238</v>
@@ -3386,7 +3386,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>18.44617080688477</v>
+        <v>18.44616889953613</v>
       </c>
       <c r="C154" t="n">
         <v>19.29999923706055</v>
@@ -3481,7 +3481,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>19.20425796508789</v>
+        <v>19.20426177978516</v>
       </c>
       <c r="C159" t="n">
         <v>19.95000076293945</v>
@@ -3500,7 +3500,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>19.14650344848633</v>
+        <v>19.14649772644043</v>
       </c>
       <c r="C160" t="n">
         <v>19.88999938964844</v>
@@ -3557,7 +3557,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>23.0460147857666</v>
+        <v>23.04601097106934</v>
       </c>
       <c r="C163" t="n">
         <v>23.8700008392334</v>
@@ -3576,7 +3576,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>25.41426086425781</v>
+        <v>25.41425895690918</v>
       </c>
       <c r="C164" t="n">
         <v>26.26000022888184</v>
@@ -3595,7 +3595,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>23.19801330566406</v>
+        <v>23.19800758361816</v>
       </c>
       <c r="C165" t="n">
         <v>23.96999931335449</v>
@@ -3633,7 +3633,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>23.66636657714844</v>
+        <v>23.66635894775391</v>
       </c>
       <c r="C167" t="n">
         <v>24.38999938964844</v>
@@ -3652,7 +3652,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>25.58761596679688</v>
+        <v>25.58761405944824</v>
       </c>
       <c r="C168" t="n">
         <v>26.3700008392334</v>
@@ -3671,7 +3671,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>25.83046340942383</v>
+        <v>25.83045768737793</v>
       </c>
       <c r="C169" t="n">
         <v>26.55999946594238</v>
@@ -3747,7 +3747,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>26.07781600952148</v>
+        <v>26.07782173156738</v>
       </c>
       <c r="C173" t="n">
         <v>26.73999977111816</v>
@@ -3766,7 +3766,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>31.81221389770508</v>
+        <v>31.81221008300781</v>
       </c>
       <c r="C174" t="n">
         <v>32.61999893188477</v>
@@ -3785,7 +3785,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>34.19178771972656</v>
+        <v>34.1917839050293</v>
       </c>
       <c r="C175" t="n">
         <v>35.06000137329102</v>
@@ -3804,7 +3804,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>35.62294387817383</v>
+        <v>35.62294769287109</v>
       </c>
       <c r="C176" t="n">
         <v>36.47000122070312</v>
@@ -3842,7 +3842,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>38.77791213989258</v>
+        <v>38.77791976928711</v>
       </c>
       <c r="C178" t="n">
         <v>39.70000076293945</v>
@@ -3861,7 +3861,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>36.6904296875</v>
+        <v>36.69043350219727</v>
       </c>
       <c r="C179" t="n">
         <v>37.5099983215332</v>
@@ -3880,7 +3880,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>45.27860641479492</v>
+        <v>45.27860260009766</v>
       </c>
       <c r="C180" t="n">
         <v>46.29000091552734</v>
@@ -3918,7 +3918,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>50.39964294433594</v>
+        <v>50.39963912963867</v>
       </c>
       <c r="C182" t="n">
         <v>51.45999908447266</v>
@@ -3937,7 +3937,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>47.28517150878906</v>
+        <v>47.28515625</v>
       </c>
       <c r="C183" t="n">
         <v>48.27999877929688</v>
@@ -3994,7 +3994,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>47.36118316650391</v>
+        <v>47.36117935180664</v>
       </c>
       <c r="C186" t="n">
         <v>48.29999923706055</v>
@@ -4013,7 +4013,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>57.19623947143555</v>
+        <v>57.19622802734375</v>
       </c>
       <c r="C187" t="n">
         <v>58.33000183105469</v>
@@ -4063,7 +4063,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>60.0642204284668</v>
+        <v>60.06421661376953</v>
       </c>
       <c r="C189" t="n">
         <v>61.18999862670898</v>
@@ -4113,7 +4113,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>67.30307006835938</v>
+        <v>67.3031005859375</v>
       </c>
       <c r="C191" t="n">
         <v>68.5</v>
@@ -4138,7 +4138,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>69.92640686035156</v>
+        <v>69.92641448974609</v>
       </c>
       <c r="C192" t="n">
         <v>71.16999816894531</v>
@@ -4163,7 +4163,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>85.96125030517578</v>
+        <v>85.96125793457031</v>
       </c>
       <c r="C193" t="n">
         <v>87.48999786376953</v>
@@ -4188,7 +4188,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>70.20247650146484</v>
+        <v>70.20249176025391</v>
       </c>
       <c r="C194" t="n">
         <v>71.40000152587891</v>
@@ -4238,7 +4238,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>70.50730133056641</v>
+        <v>70.50727844238281</v>
       </c>
       <c r="C196" t="n">
         <v>71.70999908447266</v>
@@ -4265,7 +4265,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>57.15745544433594</v>
+        <v>57.15744400024414</v>
       </c>
       <c r="C197" t="n">
         <v>58.08000183105469</v>
@@ -4292,7 +4292,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>58.21044921875</v>
+        <v>58.21045303344727</v>
       </c>
       <c r="C198" t="n">
         <v>59.15000152587891</v>
@@ -4319,7 +4319,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>42.83856582641602</v>
+        <v>42.83855819702148</v>
       </c>
       <c r="C199" t="n">
         <v>43.52999877929688</v>
@@ -4346,7 +4346,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>54.87069320678711</v>
+        <v>54.87070465087891</v>
       </c>
       <c r="C200" t="n">
         <v>55.68000030517578</v>
@@ -4373,7 +4373,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>46.13947677612305</v>
+        <v>46.13948059082031</v>
       </c>
       <c r="C201" t="n">
         <v>46.81999969482422</v>
@@ -4400,7 +4400,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>42.28631210327148</v>
+        <v>42.28630447387695</v>
       </c>
       <c r="C202" t="n">
         <v>42.90999984741211</v>
@@ -4427,7 +4427,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>39.15182876586914</v>
+        <v>39.15183258056641</v>
       </c>
       <c r="C203" t="n">
         <v>39.68000030517578</v>
@@ -4454,7 +4454,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>45.90078735351562</v>
+        <v>45.90079116821289</v>
       </c>
       <c r="C204" t="n">
         <v>46.52000045776367</v>
@@ -4481,7 +4481,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>36.54697418212891</v>
+        <v>36.54697036743164</v>
       </c>
       <c r="C205" t="n">
         <v>37.04000091552734</v>
@@ -4508,7 +4508,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>42.64553451538086</v>
+        <v>42.64553833007812</v>
       </c>
       <c r="C206" t="n">
         <v>43.15000152587891</v>
@@ -4535,7 +4535,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>44.62215042114258</v>
+        <v>44.62215805053711</v>
       </c>
       <c r="C207" t="n">
         <v>45.15000152587891</v>
@@ -4562,7 +4562,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>42.79378509521484</v>
+        <v>42.79377746582031</v>
       </c>
       <c r="C208" t="n">
         <v>43.29999923706055</v>
@@ -4589,7 +4589,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>39.07635498046875</v>
+        <v>39.07636260986328</v>
       </c>
       <c r="C209" t="n">
         <v>39.47999954223633</v>
@@ -4616,7 +4616,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>57.89199829101562</v>
+        <v>57.89200210571289</v>
       </c>
       <c r="C210" t="n">
         <v>58.4900016784668</v>
@@ -4643,7 +4643,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>59.16880798339844</v>
+        <v>59.16881942749023</v>
       </c>
       <c r="C211" t="n">
         <v>59.77999877929688</v>
@@ -4670,7 +4670,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>64.52886199951172</v>
+        <v>64.52884674072266</v>
       </c>
       <c r="C212" t="n">
         <v>65.12999725341797</v>
@@ -4697,7 +4697,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>57.71235656738281</v>
+        <v>57.71234512329102</v>
       </c>
       <c r="C213" t="n">
         <v>58.25</v>
@@ -4724,7 +4724,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>53.63037872314453</v>
+        <v>53.6303825378418</v>
       </c>
       <c r="C214" t="n">
         <v>54.13000106811523</v>
@@ -4778,7 +4778,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>55.27783203125</v>
+        <v>55.27782821655273</v>
       </c>
       <c r="C216" t="n">
         <v>55.72999954223633</v>
@@ -4805,7 +4805,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>59.82066345214844</v>
+        <v>59.8206672668457</v>
       </c>
       <c r="C217" t="n">
         <v>60.31000137329102</v>
@@ -4832,7 +4832,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>67.22176361083984</v>
+        <v>67.22175598144531</v>
       </c>
       <c r="C218" t="n">
         <v>67.69999694824219</v>
@@ -4859,7 +4859,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>71.15379333496094</v>
+        <v>71.15378570556641</v>
       </c>
       <c r="C219" t="n">
         <v>71.66000366210938</v>
@@ -4886,7 +4886,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>70.37931060791016</v>
+        <v>70.37931823730469</v>
       </c>
       <c r="C220" t="n">
         <v>70.87999725341797</v>
@@ -4913,7 +4913,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>65.49944305419922</v>
+        <v>65.49942779541016</v>
       </c>
       <c r="C221" t="n">
         <v>65.91000366210938</v>
@@ -4940,7 +4940,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>68.38136291503906</v>
+        <v>68.38137054443359</v>
       </c>
       <c r="C222" t="n">
         <v>68.80999755859375</v>
@@ -4967,7 +4967,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>69.46456909179688</v>
+        <v>69.46457672119141</v>
       </c>
       <c r="C223" t="n">
         <v>69.90000152587891</v>
@@ -4994,7 +4994,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>66.61814117431641</v>
+        <v>66.61814880371094</v>
       </c>
       <c r="C224" t="n">
         <v>66.98000335693359</v>
@@ -5048,7 +5048,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>71.73037719726562</v>
+        <v>71.73036956787109</v>
       </c>
       <c r="C226" t="n">
         <v>72.12000274658203</v>
@@ -5075,7 +5075,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>79.74315643310547</v>
+        <v>79.74317169189453</v>
       </c>
       <c r="C227" t="n">
         <v>80.11000061035156</v>
@@ -5129,7 +5129,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>109.9442291259766</v>
+        <v>109.9442367553711</v>
       </c>
       <c r="C229" t="n">
         <v>110.4499969482422</v>
@@ -5156,7 +5156,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>112.4002304077148</v>
+        <v>112.4002380371094</v>
       </c>
       <c r="C230" t="n">
         <v>112.8600006103516</v>
@@ -5210,7 +5210,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>61.31918334960938</v>
+        <v>61.31917953491211</v>
       </c>
       <c r="C232" t="n">
         <v>61.56999969482422</v>
@@ -5264,7 +5264,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>60.01290512084961</v>
+        <v>60.01290893554688</v>
       </c>
       <c r="C234" t="n">
         <v>60.18999862670898</v>
@@ -5345,7 +5345,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>62.7363395690918</v>
+        <v>62.73633575439453</v>
       </c>
       <c r="C237" t="n">
         <v>62.86999893188477</v>
@@ -5372,7 +5372,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>83.89126586914062</v>
+        <v>83.89125823974609</v>
       </c>
       <c r="C238" t="n">
         <v>84.06999969482422</v>
